--- a/artfynd/A 25082-2026 artfynd.xlsx
+++ b/artfynd/A 25082-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81395472</v>
+        <v>128609944</v>
       </c>
       <c r="B2" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>900 m NNO Höjelycke, Sk</t>
+          <t>Lerjevallen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456785.6468565261</v>
+        <v>456812</v>
       </c>
       <c r="R2" t="n">
-        <v>6229441.766609565</v>
+        <v>6229394</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-06-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-06-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,42 +758,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Invid markväg</t>
+          <t>Bokskog, block</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skånes Flora Millora 2008-2015</t>
-        </is>
-      </c>
+          <t>Örjan Fritz, Marie Glahn</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81395812</v>
+        <v>128609721</v>
       </c>
       <c r="B3" t="n">
-        <v>101854</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +793,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220461</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>With.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>900 m NNO Höjelycke, Sk</t>
+          <t>Lerjevallen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456785.6468565261</v>
+        <v>456816</v>
       </c>
       <c r="R3" t="n">
-        <v>6229441.766609565</v>
+        <v>6229391</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-07-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-07-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,85 +872,81 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Invid stig</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>6290</t>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>bokhögstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skånes Flora Millora 2008-2015</t>
-        </is>
-      </c>
+          <t>Örjan Fritz, Marie Glahn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81395583</v>
+        <v>128609078</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>750 m SSO Lilla Sandvik, Sk</t>
+          <t>Lerjevallen, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456786.864370176</v>
+        <v>456940</v>
       </c>
       <c r="R4" t="n">
-        <v>6229341.649833081</v>
+        <v>6229269</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2009-04-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2009-04-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,92 +986,73 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Skogsbacke</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Skånes Flora Millora 2008-2015</t>
-        </is>
-      </c>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129250420</v>
+        <v>128609079</v>
       </c>
       <c r="B5" t="n">
-        <v>58105</v>
+        <v>58238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lerjevallen Syd, Sk</t>
+          <t>Lerjevallen, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456753</v>
+        <v>457015</v>
       </c>
       <c r="R5" t="n">
-        <v>6229286</v>
+        <v>6229221</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1127,12 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,22 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129251054</v>
+        <v>129250420</v>
       </c>
       <c r="B6" t="n">
-        <v>58105</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1138,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1213,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456787</v>
+        <v>456753</v>
       </c>
       <c r="R6" t="n">
-        <v>6229442</v>
+        <v>6229286</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1243,12 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,6 +1221,445 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129251054</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lerjevallen Syd, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>456787</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6229442</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>81395471</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>900 m NNO Höjelycke, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>456786</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6229442</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2009-07-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2009-07-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Invid stig</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skånes Flora Millora 2008-2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>81395812</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104803</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220461</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsbräsma</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cardamine flexuosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>With.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>900 m NNO Höjelycke, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>456786</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6229442</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2009-07-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2009-07-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Invid stig</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>6290</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Skånes Flora Millora 2008-2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>81395583</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>750 m SSO Lilla Sandvik, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>456787</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6229342</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2009-04-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2009-04-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Skogsbacke</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Skånes Flora Millora 2008-2015</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25082-2026 artfynd.xlsx
+++ b/artfynd/A 25082-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128609944</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128609721</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128609078</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128609079</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129250420</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129251054</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1443,6 +1478,11 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81395471</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1554,6 +1594,11 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81395812</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,8 +1705,24 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81395583</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>